--- a/project/new/Todo Cloud S5.xlsx
+++ b/project/new/Todo Cloud S5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EVAL\1_PrestaShop\project\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004478F4-09B4-4ADB-8781-353D2B07E905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A53A754-E75C-458A-AEC0-6E5F6B53DD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12495" yWindow="0" windowWidth="12810" windowHeight="15135" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="groupe" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="95">
   <si>
     <t>ETU00XXXX</t>
   </si>
@@ -147,15 +147,6 @@
   </si>
   <si>
     <t>script de verification</t>
-  </si>
-  <si>
-    <t>ETU003296</t>
-  </si>
-  <si>
-    <t>ETU003297</t>
-  </si>
-  <si>
-    <t>ETU003298</t>
   </si>
   <si>
     <t>Protections Pages</t>
@@ -659,7 +650,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Rohy" refreshedDate="46155.379259606481" refreshedVersion="8" recordCount="46" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Rohy" refreshedDate="46155.476353356484" refreshedVersion="8" recordCount="46" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K1003" sheet="liste des taches"/>
   </cacheSource>
@@ -682,10 +673,10 @@
     <cacheField name="Qui" numFmtId="0">
       <sharedItems containsBlank="1" count="9">
         <s v="ETU003295"/>
-        <s v="ETU003296"/>
-        <s v="ETU003297"/>
-        <s v="ETU003298"/>
         <m/>
+        <s v="ETU003296" u="1"/>
+        <s v="ETU003297" u="1"/>
+        <s v="ETU003298" u="1"/>
         <s v="ETU00YYYY" u="1"/>
         <s v="ETU00XXXX" u="1"/>
         <s v="ETU00ZZZZ" u="1"/>
@@ -901,7 +892,7 @@
     <s v="ProductImport.service.ts"/>
     <s v="fonction runImport"/>
     <s v="Metier"/>
-    <x v="1"/>
+    <x v="0"/>
     <n v="100"/>
     <n v="100"/>
     <n v="0"/>
@@ -925,7 +916,7 @@
     <s v="CombinationImport.service.ts"/>
     <s v="fonction ensureAttrAndVal"/>
     <s v="Metier"/>
-    <x v="1"/>
+    <x v="0"/>
     <n v="100"/>
     <n v="100"/>
     <n v="0"/>
@@ -937,7 +928,7 @@
     <s v="CombinationImport.service.ts"/>
     <s v="fonction setStock"/>
     <s v="Metier"/>
-    <x v="2"/>
+    <x v="0"/>
     <n v="100"/>
     <n v="100"/>
     <n v="0"/>
@@ -949,7 +940,7 @@
     <s v="CombinationImport.service.ts"/>
     <s v="fonction runCombinationImport"/>
     <s v="Metier"/>
-    <x v="3"/>
+    <x v="0"/>
     <n v="100"/>
     <n v="100"/>
     <n v="0"/>
@@ -973,7 +964,7 @@
     <s v="OrderImport.service.ts"/>
     <s v="fonction"/>
     <s v="Metier"/>
-    <x v="1"/>
+    <x v="0"/>
     <n v="100"/>
     <n v="100"/>
     <n v="0"/>
@@ -985,7 +976,7 @@
     <s v="OrderImport.service.ts"/>
     <s v="fonction"/>
     <s v="Metier"/>
-    <x v="2"/>
+    <x v="0"/>
     <n v="100"/>
     <n v="100"/>
     <n v="0"/>
@@ -997,7 +988,7 @@
     <s v="OrderImport.service.ts"/>
     <s v="fonction"/>
     <s v="Metier"/>
-    <x v="3"/>
+    <x v="0"/>
     <n v="100"/>
     <n v="100"/>
     <n v="0"/>
@@ -1261,7 +1252,7 @@
     <m/>
     <m/>
     <m/>
-    <x v="4"/>
+    <x v="1"/>
     <m/>
     <m/>
     <m/>
@@ -1272,7 +1263,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="Recap" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="8" compact="0" compactData="0">
-  <location ref="A1:D8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <location ref="A1:D5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField name="Catégorie" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="Module" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
@@ -1282,14 +1273,14 @@
     <pivotField name="Qui" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
       <items count="10">
         <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
+        <item m="1" x="2"/>
+        <item m="1" x="3"/>
+        <item m="1" x="4"/>
         <item m="1" x="8"/>
         <item m="1" x="6"/>
         <item m="1" x="5"/>
         <item m="1" x="7"/>
-        <item x="4"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1301,18 +1292,9 @@
   <rowFields count="1">
     <field x="5"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="3">
     <i>
       <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i>
       <x v="8"/>
@@ -1651,7 +1633,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>37</v>
@@ -1688,10 +1670,10 @@
         <v>19</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>21</v>
@@ -1725,7 +1707,7 @@
         <v>19</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>22</v>
@@ -1762,7 +1744,7 @@
         <v>19</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>39</v>
@@ -1796,13 +1778,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>20</v>
@@ -1833,13 +1815,13 @@
         <v>18</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>21</v>
@@ -1870,13 +1852,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>23</v>
@@ -1907,13 +1889,13 @@
         <v>18</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>21</v>
@@ -1944,10 +1926,10 @@
         <v>18</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>37</v>
@@ -1981,10 +1963,10 @@
         <v>18</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>37</v>
@@ -2018,13 +2000,13 @@
         <v>18</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>21</v>
@@ -2055,13 +2037,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>23</v>
@@ -2092,13 +2074,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>21</v>
@@ -2129,13 +2111,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>21</v>
@@ -2166,13 +2148,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>21</v>
@@ -2203,13 +2185,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>21</v>
@@ -2240,13 +2222,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>21</v>
@@ -2277,13 +2259,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>21</v>
@@ -2314,13 +2296,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>21</v>
@@ -2351,13 +2333,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>21</v>
@@ -2388,13 +2370,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>21</v>
@@ -2425,13 +2407,13 @@
         <v>18</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>21</v>
@@ -2462,13 +2444,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>21</v>
@@ -2499,13 +2481,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>21</v>
@@ -2536,10 +2518,10 @@
         <v>18</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>37</v>
@@ -2573,13 +2555,13 @@
         <v>18</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>23</v>
@@ -2610,13 +2592,13 @@
         <v>18</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>21</v>
@@ -2647,13 +2629,13 @@
         <v>18</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>20</v>
@@ -2684,13 +2666,13 @@
         <v>18</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>21</v>
@@ -2721,13 +2703,13 @@
         <v>18</v>
       </c>
       <c r="C31" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="D31" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>23</v>
@@ -2755,13 +2737,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>61</v>
-      </c>
       <c r="D32" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>37</v>
@@ -2792,19 +2774,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>61</v>
-      </c>
       <c r="D33" s="31" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G33" s="31" t="s">
         <v>38</v>
@@ -2829,16 +2811,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>61</v>
-      </c>
       <c r="D34" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>23</v>
@@ -2866,13 +2848,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>61</v>
-      </c>
       <c r="D35" s="31" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>37</v>
@@ -2903,16 +2885,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>61</v>
-      </c>
       <c r="D36" s="31" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>21</v>
@@ -2940,16 +2922,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="D37" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="D37" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>64</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>21</v>
@@ -2977,16 +2959,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="7" t="s">
-        <v>61</v>
-      </c>
       <c r="D38" s="31" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>21</v>
@@ -3014,16 +2996,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="7" t="s">
-        <v>61</v>
-      </c>
       <c r="D39" s="31" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>21</v>
@@ -3051,16 +3033,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="7" t="s">
-        <v>61</v>
-      </c>
       <c r="D40" s="31" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>23</v>
@@ -3088,13 +3070,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D41" s="31" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>37</v>
@@ -3125,16 +3107,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D42" s="31" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>21</v>
@@ -3162,16 +3144,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D43" s="31" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>21</v>
@@ -3199,16 +3181,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C44" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="7" t="s">
         <v>93</v>
-      </c>
-      <c r="D44" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>96</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>21</v>
@@ -3236,16 +3218,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D45" s="31" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>23</v>
@@ -3273,13 +3255,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D46" s="31" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
@@ -3342,10 +3324,10 @@
         <v>38</v>
       </c>
       <c r="B3" s="32">
-        <v>3800</v>
+        <v>4500</v>
       </c>
       <c r="C3" s="33">
-        <v>3800</v>
+        <v>4500</v>
       </c>
       <c r="D3" s="34">
         <v>0</v>
@@ -3353,68 +3335,28 @@
     </row>
     <row r="4" spans="1:4" ht="12.75">
       <c r="A4" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="35">
-        <v>300</v>
-      </c>
-      <c r="C4" s="36">
-        <v>300</v>
-      </c>
-      <c r="D4" s="37">
-        <v>0</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37"/>
     </row>
     <row r="5" spans="1:4" ht="12.75">
-      <c r="A5" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="35">
-        <v>200</v>
-      </c>
-      <c r="C5" s="36">
-        <v>200</v>
-      </c>
-      <c r="D5" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="12.75">
-      <c r="A6" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="35">
-        <v>200</v>
-      </c>
-      <c r="C6" s="36">
-        <v>200</v>
-      </c>
-      <c r="D6" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="12.75">
-      <c r="A7" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="37"/>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A8" s="30" t="s">
+      <c r="A5" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="38">
+      <c r="B5" s="38">
         <v>4500</v>
       </c>
-      <c r="C8" s="39">
+      <c r="C5" s="39">
         <v>4500</v>
       </c>
-      <c r="D8" s="40">
-        <v>0</v>
-      </c>
-    </row>
+      <c r="D5" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="12.75"/>
+    <row r="7" spans="1:4" ht="12.75"/>
     <row r="12" spans="1:4" ht="12.75">
       <c r="A12" s="11" t="s">
         <v>17</v>
